--- a/src/test/resources/Project.xlsx
+++ b/src/test/resources/Project.xlsx
@@ -1,22 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Downloads\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC232AFA-CCB8-497C-868B-E93F2EDD6242}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:801_{9E89BD52-7ED3-4968-AB3C-7580F4CA3796}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{E064F476-51E8-4BC7-AB0D-1C79CD4BA36E}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{E064F476-51E8-4BC7-AB0D-1C79CD4BA36E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="0"/>
+  <oleSize ref="A16:N31"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -544,13 +540,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6B8674B-EEEF-45A7-9C3E-8B7F61F50A67}">
   <dimension ref="A1:B34"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
-    <col min="2" max="2" width="27.81640625" customWidth="1"/>
+    <col min="2" max="2" width="27.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -558,7 +554,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -566,7 +562,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>3</v>
       </c>
@@ -574,7 +570,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>4</v>
       </c>
@@ -582,7 +578,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
@@ -590,7 +586,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>6</v>
       </c>
@@ -598,7 +594,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>7</v>
       </c>
@@ -606,7 +602,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>2</v>
       </c>
@@ -614,7 +610,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>3</v>
       </c>
@@ -622,7 +618,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>4</v>
       </c>
@@ -630,7 +626,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>5</v>
       </c>
@@ -638,7 +634,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
         <v>6</v>
       </c>
@@ -646,7 +642,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
         <v>7</v>
       </c>
@@ -654,7 +650,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
         <v>15</v>
       </c>
@@ -662,7 +658,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
         <v>16</v>
       </c>
@@ -670,7 +666,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
         <v>17</v>
       </c>
@@ -678,7 +674,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
         <v>18</v>
       </c>
@@ -686,7 +682,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
         <v>15</v>
       </c>
@@ -694,7 +690,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
         <v>18</v>
       </c>
@@ -702,7 +698,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
         <v>17</v>
       </c>
@@ -710,7 +706,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
         <v>16</v>
       </c>
@@ -718,7 +714,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
         <v>23</v>
       </c>
@@ -726,7 +722,7 @@
         <v>1234</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
         <v>24</v>
       </c>
@@ -734,7 +730,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
         <v>25</v>
       </c>
@@ -742,7 +738,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
         <v>26</v>
       </c>
@@ -750,27 +746,27 @@
         <v>232121</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>1243211</v>
       </c>
@@ -778,7 +774,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
         <v>29</v>
       </c>
@@ -786,7 +782,7 @@
         <v>1242</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
         <v>30</v>
       </c>
@@ -794,7 +790,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B34" t="s">
         <v>8</v>
       </c>
@@ -818,77 +814,77 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA123EB5-84C5-4D07-82F0-12B894BA0878}">
   <dimension ref="A1:A15"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="45.08984375" customWidth="1"/>
+    <col min="1" max="1" width="45.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>44</v>
       </c>

--- a/src/test/resources/Project.xlsx
+++ b/src/test/resources/Project.xlsx
@@ -3,28 +3,19 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:801_{9E89BD52-7ED3-4968-AB3C-7580F4CA3796}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:801_{8AA214FF-7A00-4A94-8243-4D5D8A54BF08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{E064F476-51E8-4BC7-AB0D-1C79CD4BA36E}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{E064F476-51E8-4BC7-AB0D-1C79CD4BA36E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="0"/>
-  <oleSize ref="A16:N31"/>
+  <oleSize ref="A1:O11"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -123,9 +114,6 @@
     <t>12@321</t>
   </si>
   <si>
-    <t>####@</t>
-  </si>
-  <si>
     <t>ProductsName</t>
   </si>
   <si>
@@ -166,6 +154,9 @@
   </si>
   <si>
     <t>Mobiles</t>
+  </si>
+  <si>
+    <t>h####@</t>
   </si>
 </sst>
 </file>
@@ -217,10 +208,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -606,7 +596,7 @@
       <c r="A8" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" t="s">
         <v>9</v>
       </c>
     </row>
@@ -614,7 +604,7 @@
       <c r="A9" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B9" t="s">
         <v>10</v>
       </c>
     </row>
@@ -622,7 +612,7 @@
       <c r="A10" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B10" t="s">
         <v>11</v>
       </c>
     </row>
@@ -686,7 +676,7 @@
       <c r="A18" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B18" s="2" t="s">
+      <c r="B18" t="s">
         <v>19</v>
       </c>
     </row>
@@ -694,7 +684,7 @@
       <c r="A19" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B19" s="2" t="s">
+      <c r="B19" t="s">
         <v>20</v>
       </c>
     </row>
@@ -702,7 +692,7 @@
       <c r="A20" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B20" s="2" t="s">
+      <c r="B20" t="s">
         <v>21</v>
       </c>
     </row>
@@ -775,7 +765,7 @@
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A32" s="2" t="s">
+      <c r="A32" t="s">
         <v>29</v>
       </c>
       <c r="B32">
@@ -783,10 +773,10 @@
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A33" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="B33" s="2" t="s">
+      <c r="A33" t="s">
+        <v>44</v>
+      </c>
+      <c r="B33" t="s">
         <v>19</v>
       </c>
     </row>
@@ -796,24 +786,13 @@
       </c>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="B8" r:id="rId1" xr:uid="{B839975D-F635-4EF3-A1B8-AD1E8392E861}"/>
-    <hyperlink ref="B9" r:id="rId2" xr:uid="{91B451BF-CC8A-43D0-AD53-9A6666966643}"/>
-    <hyperlink ref="B10" r:id="rId3" xr:uid="{61263C78-CBB7-41AD-8E3D-CD4B48880A0F}"/>
-    <hyperlink ref="B18" r:id="rId4" xr:uid="{F696C918-407C-4B6D-BA14-D28C1D7F2177}"/>
-    <hyperlink ref="B19" r:id="rId5" xr:uid="{FB2ACDAF-E269-4315-A08D-8DE4243A9B42}"/>
-    <hyperlink ref="B20" r:id="rId6" xr:uid="{7F3BA177-0D51-4B85-A383-E26C0EFFF203}"/>
-    <hyperlink ref="A32" r:id="rId7" xr:uid="{333EF0B3-3D2D-45F9-AC61-1978BE9AC49C}"/>
-    <hyperlink ref="A33" r:id="rId8" xr:uid="{7CCA8945-610B-400D-92B1-B96DC4C6DB23}"/>
-    <hyperlink ref="B33" r:id="rId9" xr:uid="{76D1DC96-5316-42EB-88AA-B9D35C54C4CC}"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA123EB5-84C5-4D07-82F0-12B894BA0878}">
-  <dimension ref="A1:A15"/>
+  <dimension ref="A1:A14"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="45.109375" customWidth="1"/>
@@ -821,36 +800,41 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
         <v>35</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A6" s="3" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
         <v>37</v>
       </c>
     </row>
@@ -882,11 +866,6 @@
     <row r="14" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>43</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
-        <v>44</v>
       </c>
     </row>
   </sheetData>

--- a/src/test/resources/Project.xlsx
+++ b/src/test/resources/Project.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:801_{8AA214FF-7A00-4A94-8243-4D5D8A54BF08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:801_{F2844885-2EB9-4D96-AD8C-1EAE6AD8245F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{E064F476-51E8-4BC7-AB0D-1C79CD4BA36E}"/>
   </bookViews>
@@ -12,7 +12,7 @@
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="0"/>
-  <oleSize ref="A1:O11"/>
+  <oleSize ref="A1:M14"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="35">
   <si>
     <t>UserName</t>
   </si>
@@ -120,40 +120,10 @@
     <t>Sauce Labs Backpack</t>
   </si>
   <si>
-    <t>Sauce Labs Bolt T-Shirt</t>
-  </si>
-  <si>
     <t>Sauce Labs Bike Light</t>
   </si>
   <si>
-    <t>Sauce Labs Fleece Jacket</t>
-  </si>
-  <si>
-    <t>Sauce Labs Onesie</t>
-  </si>
-  <si>
     <t>Test.allTheThings() T-Shirt (Red)</t>
-  </si>
-  <si>
-    <t>Bag</t>
-  </si>
-  <si>
-    <t>Shirt</t>
-  </si>
-  <si>
-    <t>Bat</t>
-  </si>
-  <si>
-    <t>Shoees</t>
-  </si>
-  <si>
-    <t>crocs</t>
-  </si>
-  <si>
-    <t>Laptop</t>
-  </si>
-  <si>
-    <t>Mobiles</t>
   </si>
   <si>
     <t>h####@</t>
@@ -163,7 +133,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -177,14 +147,6 @@
       <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="10"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -204,19 +166,14 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -774,7 +731,7 @@
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="B33" t="s">
         <v>19</v>
@@ -808,70 +765,27 @@
         <v>31</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A6" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
-        <v>43</v>
-      </c>
-    </row>
+    <row r="5" spans="1:1" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="6" spans="1:1" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="7" spans="1:1" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="8" spans="1:1" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="9" spans="1:1" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="10" spans="1:1" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="11" spans="1:1" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="12" spans="1:1" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="13" spans="1:1" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="14" spans="1:1" customFormat="1" x14ac:dyDescent="0.3"/>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="A6" r:id="rId1" display="https://www.saucedemo.com/inventory.html" xr:uid="{B8D41060-2B04-42D8-B6A3-338B12655779}"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>